--- a/src/data/rules.xlsx
+++ b/src/data/rules.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>recommendation</t>
   </si>
@@ -60,6 +60,15 @@
   </si>
   <si>
     <t>puliza data ndani</t>
+  </si>
+  <si>
+    <t>njano, hukauka, madoa</t>
+  </si>
+  <si>
+    <t>kukosa mbolea</t>
+  </si>
+  <si>
+    <t>weka mbolea kwenye kila muhindi kwa kuzingatia utaratubu wa kila maellezeko</t>
   </si>
 </sst>
 </file>
@@ -377,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -420,6 +429,20 @@
       </c>
       <c r="D3" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
